--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486829_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486829_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MORENO CASTRO</t>
+          <t>P. RODRIGUEZ FAJARDO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7874</v>
+        <v>1.7659</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4355</v>
+        <v>1.5268</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2229</v>
+        <v>0.2391</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3574</v>
+        <v>-1.0391</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7244</v>
+        <v>-1.0686</v>
       </c>
       <c r="I2" t="n">
-        <v>0.633</v>
+        <v>0.0294</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6682</v>
+        <v>0.1065</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2763</v>
+        <v>-0.3096</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6081</v>
+        <v>0.4161</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6892</v>
+        <v>-1.1456</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.759</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2411</v>
+        <v>-0.3866</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.1585</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4301</v>
+        <v>0.8273</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0548</v>
+        <v>0.1926</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3752</v>
+        <v>0.6347</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.8193</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.4084</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. HERNÁNDEZ CHÁVEZ</t>
+          <t>J. MORENO CASTRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4997</v>
+        <v>1.7365</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9932</v>
+        <v>-0.6354</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5065</v>
+        <v>2.3719</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4313</v>
+        <v>1.3574</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7244</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7211</v>
+        <v>0.633</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1494</v>
+        <v>0.6682</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6761</v>
+        <v>1.2763</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.6081</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2819</v>
+        <v>0.6892</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9659</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2478</v>
+        <v>1.2411</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R3" t="n">
         <v>1.1585</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7391</v>
+        <v>0.3792</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2487</v>
+        <v>-0.1451</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9878</v>
+        <v>0.5242</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.6361</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.9217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ FAJARDO</t>
+          <t>R. HERNÁNDEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0984</v>
+        <v>1.3536</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0579</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0405</v>
+        <v>0.4569</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0391</v>
+        <v>1.4313</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0686</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0294</v>
+        <v>0.7211</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1065</v>
+        <v>1.1494</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3096</v>
+        <v>1.6761</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4161</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1456</v>
+        <v>0.2819</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.759</v>
+        <v>-0.9659</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3866</v>
+        <v>1.2478</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R4" t="n">
         <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1597</v>
+        <v>0.5929</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2763</v>
+        <v>-0.3452</v>
       </c>
       <c r="U4" t="n">
-        <v>0.436</v>
+        <v>0.9382</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8193</v>
+        <v>-1.6361</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4084</v>
+        <v>-1.9217</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2806</v>
+        <v>0.1579</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1249</v>
+        <v>-0.1731</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4055</v>
+        <v>0.331</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7178</v>
@@ -844,13 +844,13 @@
         <v>0.1931</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8054</v>
+        <v>0.6826</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5239</v>
+        <v>0.4757</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2814</v>
+        <v>0.2069</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. GRIMA LORENZO</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0571</v>
+        <v>-0.4343</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2832</v>
+        <v>0.353</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.3404</v>
+        <v>-0.7873</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1436</v>
+        <v>-0.5649</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4202</v>
+        <v>-0.2485</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7234</v>
+        <v>-0.3165</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8506</v>
+        <v>1.1256</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2357</v>
+        <v>0.5107</v>
       </c>
       <c r="L6" t="n">
         <v>0.615</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9942</v>
+        <v>-1.6906</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6558</v>
+        <v>-0.7591</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3384</v>
+        <v>-0.9314</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.3862</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-1.1585</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-1.9308</v>
       </c>
       <c r="R6" t="n">
         <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4103</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1783</v>
+        <v>0.3858</v>
       </c>
       <c r="U6" t="n">
-        <v>0.232</v>
+        <v>0.4968</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1654</v>
+        <v>-0.3658</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1851</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3505</v>
+        <v>-0.3658</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>P. GRIMA LORENZO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5873</v>
+        <v>-1.0333</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5848</v>
+        <v>2.2077</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0025</v>
+        <v>-3.241</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5649</v>
+        <v>-1.1436</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2485</v>
+        <v>-0.4202</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3165</v>
+        <v>-0.7234</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1256</v>
+        <v>1.8506</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5107</v>
+        <v>1.2357</v>
       </c>
       <c r="L7" t="n">
         <v>0.615</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6906</v>
+        <v>-2.9942</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7591</v>
+        <v>-1.6558</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9314</v>
+        <v>-1.3384</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3862</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1585</v>
+        <v>-1.9308</v>
       </c>
       <c r="R7" t="n">
         <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2704</v>
+        <v>1.4341</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5518999999999999</v>
+        <v>1.1028</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2815</v>
+        <v>0.3313</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3658</v>
+        <v>-0.1654</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1851</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3658</v>
+        <v>-1.3505</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. GONZALEZ-MONJE PEREZ</t>
+          <t>A. BRASSEUR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9287</v>
+        <v>-1.5673</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.5185</v>
+        <v>-1.9667</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5897</v>
+        <v>0.3995</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.636</v>
+        <v>-2.1947</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.276</v>
+        <v>-1.7449</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.36</v>
+        <v>-0.4498</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.9113</v>
+        <v>-1.7114</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.586</v>
+        <v>-0.2963</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.3253</v>
+        <v>-1.4151</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2753</v>
+        <v>-0.4833</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6899</v>
+        <v>-1.4486</v>
       </c>
       <c r="O8" t="n">
         <v>0.9653</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>0.629</v>
+        <v>-0.1448</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6071</v>
+        <v>-0.0622</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2361</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0801</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BRASSEUR</t>
+          <t>M. GONZALEZ-MONJE PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0349</v>
+        <v>-1.7509</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2357</v>
+        <v>-4.0426</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2008</v>
+        <v>2.2917</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1947</v>
+        <v>-3.636</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7449</v>
+        <v>-1.276</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4498</v>
+        <v>-2.36</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7114</v>
+        <v>-3.9113</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2963</v>
+        <v>-0.586</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4151</v>
+        <v>-3.3253</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4833</v>
+        <v>0.2753</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4486</v>
+        <v>-0.6899</v>
       </c>
       <c r="O9" t="n">
         <v>0.9653</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6125</v>
+        <v>0.8068</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3312</v>
+        <v>-0.1313</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2813</v>
+        <v>0.9381</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.0801</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.0801</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. SOW</t>
+          <t>J. PARRONDO CASTRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5054</v>
+        <v>-2.3193</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7584</v>
+        <v>0.2197</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.747</v>
+        <v>-2.539</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2899</v>
+        <v>-1.7842</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.164</v>
+        <v>-0.8618</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1258</v>
+        <v>-0.9224</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8408</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9222</v>
+        <v>0.725</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0814</v>
+        <v>0.0023</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4491</v>
+        <v>-2.5115</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2418</v>
+        <v>-1.5868</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2072</v>
+        <v>-0.9247</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1931</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="R10" t="n">
         <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2631</v>
+        <v>0.1793</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0477</v>
+        <v>-0.2486</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2154</v>
+        <v>0.4279</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2856</v>
+        <v>-0.3282</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PARRONDO CASTRO</t>
+          <t>S. SOW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5702</v>
+        <v>-2.755</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3044</v>
+        <v>-0.9583</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2658</v>
+        <v>-1.7967</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7842</v>
+        <v>-3.2899</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8618</v>
+        <v>-2.164</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9224</v>
+        <v>-1.1258</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7272999999999999</v>
+        <v>-0.8408</v>
       </c>
       <c r="K11" t="n">
-        <v>0.725</v>
+        <v>-0.9222</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0023</v>
+        <v>0.0814</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5115</v>
+        <v>-2.4491</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5868</v>
+        <v>-1.2418</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9247</v>
+        <v>-1.2072</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3862</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="R11" t="n">
         <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0716</v>
+        <v>1.0136</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.8478</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.1657</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3282</v>
+        <v>-0.2856</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2674</v>
+        <v>-3.0178</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2143</v>
+        <v>-1.8901</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0532</v>
+        <v>-1.1277</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5185</v>
@@ -1390,13 +1390,13 @@
         <v>0.7723</v>
       </c>
       <c r="S12" t="n">
-        <v>0.309</v>
+        <v>0.5586</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1933</v>
+        <v>0.1308</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5023</v>
+        <v>0.4278</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8995</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.284899999999999</v>
+        <v>-7.864000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.842200000000002</v>
+        <v>-4.4623</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.443</v>
+        <v>-3.401599999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-13.1</v>
@@ -1438,13 +1438,13 @@
         <v>-8.2738</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.8263</v>
+        <v>-4.826300000000001</v>
       </c>
       <c r="J13" t="n">
         <v>-1.5749</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7651</v>
+        <v>2.765099999999999</v>
       </c>
       <c r="L13" t="n">
         <v>-4.3397</v>
@@ -1456,7 +1456,7 @@
         <v>-11.0385</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4863999999999998</v>
+        <v>-0.4864000000000002</v>
       </c>
       <c r="P13" t="n">
         <v>0.9653</v>
@@ -1468,13 +1468,13 @@
         <v>9.654</v>
       </c>
       <c r="S13" t="n">
-        <v>5.791199999999999</v>
+        <v>7.2122</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8235000000000003</v>
+        <v>2.2031</v>
       </c>
       <c r="U13" t="n">
-        <v>4.9675</v>
+        <v>5.009000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-2.9414</v>
@@ -1483,7 +1483,7 @@
         <v>3.5979</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.539299999999999</v>
+        <v>-6.5393</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4067</v>
+        <v>5.5613</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9587</v>
+        <v>5.7518</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.552</v>
+        <v>-0.1906</v>
       </c>
       <c r="G14" t="n">
         <v>2.8237</v>
@@ -1546,13 +1546,13 @@
         <v>0.9654</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0386</v>
+        <v>0.1932</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1377</v>
+        <v>-0.0692</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.099</v>
+        <v>0.2624</v>
       </c>
       <c r="V14" t="n">
         <v>1.5789</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5788</v>
+        <v>3.0296</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8169</v>
+        <v>2.1272</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7619</v>
+        <v>0.9024</v>
       </c>
       <c r="G15" t="n">
         <v>4.6334</v>
@@ -1624,13 +1624,13 @@
         <v>1.1585</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.5033</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8829</v>
+        <v>-0.5726</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0711</v>
+        <v>0.0694</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3282</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.285</v>
+        <v>2.7002</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1318</v>
+        <v>1.2353</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1532</v>
+        <v>1.4649</v>
       </c>
       <c r="G16" t="n">
         <v>1.4204</v>
@@ -1702,13 +1702,13 @@
         <v>0.5792</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6564</v>
+        <v>-0.2413</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6622</v>
+        <v>-0.5588</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0058</v>
+        <v>0.3175</v>
       </c>
       <c r="V16" t="n">
         <v>1.9072</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2072</v>
+        <v>2.3755</v>
       </c>
       <c r="E17" t="n">
-        <v>2.424</v>
+        <v>2.2171</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2167</v>
+        <v>0.1584</v>
       </c>
       <c r="G17" t="n">
         <v>2.885</v>
@@ -1780,13 +1780,13 @@
         <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2648</v>
+        <v>-0.0965</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0279</v>
+        <v>-0.2347</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2369</v>
+        <v>0.1383</v>
       </c>
       <c r="V17" t="n">
         <v>-0.22</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.873</v>
+        <v>2.1032</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0035</v>
+        <v>0.1069</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8695</v>
+        <v>1.9963</v>
       </c>
       <c r="G18" t="n">
         <v>1.8823</v>
@@ -1858,13 +1858,13 @@
         <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6231</v>
+        <v>-0.3929</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8277</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2046</v>
+        <v>0.3314</v>
       </c>
       <c r="V18" t="n">
         <v>0.6138</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>G. MUKENDI KABANGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0901</v>
+        <v>0.527</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0745</v>
+        <v>-0.3098</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1646</v>
+        <v>0.8368</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6771</v>
+        <v>2.2541</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0275</v>
+        <v>0.8209</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3504</v>
+        <v>1.4332</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3128</v>
+        <v>2.0902</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9593</v>
+        <v>1.2357</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6465</v>
+        <v>0.8545</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3643</v>
+        <v>0.1639</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0682</v>
+        <v>-0.4148</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2961</v>
+        <v>0.5786</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R19" t="n">
         <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7447</v>
+        <v>-0.8274</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1934</v>
+        <v>-0.4692</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5513</v>
+        <v>-0.3581</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1577</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7716</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6138</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3934</v>
+        <v>0.0764</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7464</v>
+        <v>-0.4882</v>
       </c>
       <c r="F20" t="n">
-        <v>1.353</v>
+        <v>0.5645</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7197</v>
+        <v>0.6771</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5168</v>
+        <v>1.0275</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2366</v>
+        <v>-0.3504</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8083</v>
+        <v>0.3128</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1381</v>
+        <v>0.9593</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9464</v>
+        <v>-0.6465</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0885</v>
+        <v>0.3643</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6212</v>
+        <v>0.0682</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7098</v>
+        <v>0.2961</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7393999999999999</v>
+        <v>-0.7585</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0273</v>
+        <v>-0.6071</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7121</v>
+        <v>-0.1513</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.22</v>
+        <v>0.1577</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.7716</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.22</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. MUKENDI KABANGA</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8356</v>
+        <v>-0.6224</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7235</v>
+        <v>-1.9532</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1121</v>
+        <v>1.3308</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2541</v>
+        <v>-0.7197</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8209</v>
+        <v>0.5168</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4332</v>
+        <v>-1.2366</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0902</v>
+        <v>-0.8083</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2357</v>
+        <v>1.1381</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8545</v>
+        <v>-1.9464</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1639</v>
+        <v>0.0885</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4148</v>
+        <v>-0.6212</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5786</v>
+        <v>0.7098</v>
       </c>
       <c r="P21" t="n">
+        <v>-0.1931</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-0.9654</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.9308</v>
-      </c>
       <c r="R21" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.19</v>
+        <v>0.5104</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8829</v>
+        <v>-0.1795</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.307</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.22</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6272</v>
+        <v>-1.7514</v>
       </c>
       <c r="E22" t="n">
         <v>-3.075</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4478</v>
+        <v>1.3236</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3996</v>
@@ -2170,13 +2170,13 @@
         <v>0.7723</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0001</v>
+        <v>-0.1241</v>
       </c>
       <c r="T22" t="n">
         <v>-0.6622</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6622</v>
+        <v>0.5381</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2998</v>
+        <v>-1.9565</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2727</v>
+        <v>-2.1693</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0271</v>
+        <v>0.2128</v>
       </c>
       <c r="G23" t="n">
         <v>-0.3566</v>
@@ -2248,13 +2248,13 @@
         <v>0.7723</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1362</v>
+        <v>-0.7929</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9933</v>
+        <v>-0.8899</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1429</v>
+        <v>0.0969</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.284800000000001</v>
+        <v>12.0429</v>
       </c>
       <c r="E24" t="n">
-        <v>3.4428</v>
+        <v>3.442800000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>5.8421</v>
+        <v>8.5999</v>
       </c>
       <c r="G24" t="n">
         <v>13.1001</v>
@@ -2326,13 +2326,13 @@
         <v>8.688499999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.7912</v>
+        <v>-3.0333</v>
       </c>
       <c r="T24" t="n">
         <v>-4.9675</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8235</v>
+        <v>1.9346</v>
       </c>
       <c r="V24" t="n">
         <v>2.9412</v>
